--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528290</v>
+        <v>123528200</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480646</v>
+        <v>480609</v>
       </c>
       <c r="R2" t="n">
-        <v>6597107</v>
+        <v>6597045</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,17 +756,13 @@
           <t>2025-03-27</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528192</v>
+        <v>123528299</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>78867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,58 +793,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480611</v>
+        <v>480658</v>
       </c>
       <c r="R3" t="n">
-        <v>6597066</v>
+        <v>6597117</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528299</v>
+        <v>123528169</v>
       </c>
       <c r="B4" t="n">
-        <v>78861</v>
+        <v>79399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480658</v>
+        <v>480651</v>
       </c>
       <c r="R4" t="n">
-        <v>6597117</v>
+        <v>6596942</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528200</v>
+        <v>123528420</v>
       </c>
       <c r="B5" t="n">
-        <v>90931</v>
+        <v>78867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480609</v>
+        <v>480700</v>
       </c>
       <c r="R5" t="n">
-        <v>6597045</v>
+        <v>6597049</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528420</v>
+        <v>123528336</v>
       </c>
       <c r="B6" t="n">
-        <v>78861</v>
+        <v>78867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480700</v>
+        <v>480674</v>
       </c>
       <c r="R6" t="n">
-        <v>6597049</v>
+        <v>6597089</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,7 +1208,7 @@
         <v>123528399</v>
       </c>
       <c r="B7" t="n">
-        <v>78934</v>
+        <v>78940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,42 +1324,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528169</v>
+        <v>123528290</v>
       </c>
       <c r="B8" t="n">
-        <v>79393</v>
+        <v>56697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480651</v>
+        <v>480646</v>
       </c>
       <c r="R8" t="n">
-        <v>6596942</v>
+        <v>6597107</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,13 +1414,17 @@
           <t>2025-03-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,53 +1443,70 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528336</v>
+        <v>123528192</v>
       </c>
       <c r="B9" t="n">
-        <v>78861</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480674</v>
+        <v>480611</v>
       </c>
       <c r="R9" t="n">
-        <v>6597089</v>
+        <v>6597066</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528200</v>
+        <v>123528399</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>78945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480609</v>
+        <v>480697</v>
       </c>
       <c r="R2" t="n">
-        <v>6597045</v>
+        <v>6597053</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +797,7 @@
         <v>123528299</v>
       </c>
       <c r="B3" t="n">
-        <v>78867</v>
+        <v>78872</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528169</v>
+        <v>123528420</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>78872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480651</v>
+        <v>480700</v>
       </c>
       <c r="R4" t="n">
-        <v>6596942</v>
+        <v>6597049</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528420</v>
+        <v>123528200</v>
       </c>
       <c r="B5" t="n">
-        <v>78867</v>
+        <v>90953</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480700</v>
+        <v>480609</v>
       </c>
       <c r="R5" t="n">
-        <v>6597049</v>
+        <v>6597045</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1115,7 @@
         <v>123528336</v>
       </c>
       <c r="B6" t="n">
-        <v>78867</v>
+        <v>78872</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528399</v>
+        <v>123528169</v>
       </c>
       <c r="B7" t="n">
-        <v>78940</v>
+        <v>79404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,37 +1230,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1256,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480697</v>
+        <v>480651</v>
       </c>
       <c r="R7" t="n">
-        <v>6597053</v>
+        <v>6596942</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,11 +1297,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
         <v>123528290</v>
       </c>
       <c r="B8" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>123528192</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123528399</v>
       </c>
       <c r="B2" t="n">
-        <v>78945</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528299</v>
+        <v>123528200</v>
       </c>
       <c r="B3" t="n">
-        <v>78872</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480658</v>
+        <v>480609</v>
       </c>
       <c r="R3" t="n">
-        <v>6597117</v>
+        <v>6597045</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,7 +903,7 @@
         <v>123528420</v>
       </c>
       <c r="B4" t="n">
-        <v>78872</v>
+        <v>78874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528200</v>
+        <v>123528169</v>
       </c>
       <c r="B5" t="n">
-        <v>90953</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480609</v>
+        <v>480651</v>
       </c>
       <c r="R5" t="n">
-        <v>6597045</v>
+        <v>6596942</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528336</v>
+        <v>123528299</v>
       </c>
       <c r="B6" t="n">
-        <v>78872</v>
+        <v>78874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480674</v>
+        <v>480658</v>
       </c>
       <c r="R6" t="n">
-        <v>6597089</v>
+        <v>6597117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528169</v>
+        <v>123528336</v>
       </c>
       <c r="B7" t="n">
-        <v>79404</v>
+        <v>78874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480651</v>
+        <v>480674</v>
       </c>
       <c r="R7" t="n">
-        <v>6596942</v>
+        <v>6597089</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,62 +1324,70 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528290</v>
+        <v>123528192</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480646</v>
+        <v>480611</v>
       </c>
       <c r="R8" t="n">
-        <v>6597107</v>
+        <v>6597066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,11 +1420,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,70 +1446,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528192</v>
+        <v>123528290</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480611</v>
+        <v>480646</v>
       </c>
       <c r="R9" t="n">
-        <v>6597066</v>
+        <v>6597107</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528399</v>
+        <v>123528169</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480697</v>
+        <v>480651</v>
       </c>
       <c r="R2" t="n">
-        <v>6597053</v>
+        <v>6596942</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528200</v>
+        <v>123528399</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,29 +793,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480609</v>
+        <v>480697</v>
       </c>
       <c r="R3" t="n">
-        <v>6597045</v>
+        <v>6597053</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528169</v>
+        <v>123528336</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>78874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480651</v>
+        <v>480674</v>
       </c>
       <c r="R5" t="n">
-        <v>6596942</v>
+        <v>6597089</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528336</v>
+        <v>123528200</v>
       </c>
       <c r="B7" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480674</v>
+        <v>480609</v>
       </c>
       <c r="R7" t="n">
-        <v>6597089</v>
+        <v>6597045</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,70 +1324,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528192</v>
+        <v>123528290</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480611</v>
+        <v>480646</v>
       </c>
       <c r="R8" t="n">
-        <v>6597066</v>
+        <v>6597107</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,6 +1412,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,62 +1443,70 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528290</v>
+        <v>123528192</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480646</v>
+        <v>480611</v>
       </c>
       <c r="R9" t="n">
-        <v>6597107</v>
+        <v>6597066</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,11 +1539,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528399</v>
+        <v>123528420</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>78874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480697</v>
+        <v>480700</v>
       </c>
       <c r="R3" t="n">
-        <v>6597053</v>
+        <v>6597049</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +860,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528420</v>
+        <v>123528399</v>
       </c>
       <c r="B4" t="n">
-        <v>78874</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,29 +899,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480700</v>
+        <v>480697</v>
       </c>
       <c r="R4" t="n">
-        <v>6597049</v>
+        <v>6597053</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528336</v>
+        <v>123528299</v>
       </c>
       <c r="B5" t="n">
         <v>78874</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480674</v>
+        <v>480658</v>
       </c>
       <c r="R5" t="n">
-        <v>6597089</v>
+        <v>6597117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528299</v>
+        <v>123528200</v>
       </c>
       <c r="B6" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480658</v>
+        <v>480609</v>
       </c>
       <c r="R6" t="n">
-        <v>6597117</v>
+        <v>6597045</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528200</v>
+        <v>123528336</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>78874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480609</v>
+        <v>480674</v>
       </c>
       <c r="R7" t="n">
-        <v>6597045</v>
+        <v>6597089</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,62 +1324,70 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528290</v>
+        <v>123528192</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480646</v>
+        <v>480611</v>
       </c>
       <c r="R8" t="n">
-        <v>6597107</v>
+        <v>6597066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,11 +1420,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,70 +1446,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528192</v>
+        <v>123528290</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480611</v>
+        <v>480646</v>
       </c>
       <c r="R9" t="n">
-        <v>6597066</v>
+        <v>6597107</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528169</v>
+        <v>123528336</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480651</v>
+        <v>480674</v>
       </c>
       <c r="R2" t="n">
-        <v>6596942</v>
+        <v>6597089</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528420</v>
+        <v>123528299</v>
       </c>
       <c r="B3" t="n">
         <v>78874</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480700</v>
+        <v>480658</v>
       </c>
       <c r="R3" t="n">
-        <v>6597049</v>
+        <v>6597117</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528399</v>
+        <v>123528169</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,37 +899,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480697</v>
+        <v>480651</v>
       </c>
       <c r="R4" t="n">
-        <v>6597053</v>
+        <v>6596942</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528299</v>
+        <v>123528420</v>
       </c>
       <c r="B5" t="n">
         <v>78874</v>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480658</v>
+        <v>480700</v>
       </c>
       <c r="R5" t="n">
-        <v>6597117</v>
+        <v>6597049</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528200</v>
+        <v>123528399</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,29 +1111,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480609</v>
+        <v>480697</v>
       </c>
       <c r="R6" t="n">
-        <v>6597045</v>
+        <v>6597053</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1191,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528336</v>
+        <v>123528200</v>
       </c>
       <c r="B7" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480674</v>
+        <v>480609</v>
       </c>
       <c r="R7" t="n">
-        <v>6597089</v>
+        <v>6597045</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,70 +1324,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528192</v>
+        <v>123528290</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480611</v>
+        <v>480646</v>
       </c>
       <c r="R8" t="n">
-        <v>6597066</v>
+        <v>6597107</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,6 +1412,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,62 +1443,70 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528290</v>
+        <v>123528192</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480646</v>
+        <v>480611</v>
       </c>
       <c r="R9" t="n">
-        <v>6597107</v>
+        <v>6597066</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,11 +1539,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528336</v>
+        <v>123528169</v>
       </c>
       <c r="B2" t="n">
-        <v>78874</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480674</v>
+        <v>480651</v>
       </c>
       <c r="R2" t="n">
-        <v>6597089</v>
+        <v>6596942</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528299</v>
+        <v>123528336</v>
       </c>
       <c r="B3" t="n">
         <v>78874</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480658</v>
+        <v>480674</v>
       </c>
       <c r="R3" t="n">
-        <v>6597117</v>
+        <v>6597089</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528169</v>
+        <v>123528420</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>78874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480651</v>
+        <v>480700</v>
       </c>
       <c r="R4" t="n">
-        <v>6596942</v>
+        <v>6597049</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528420</v>
+        <v>123528200</v>
       </c>
       <c r="B5" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480700</v>
+        <v>480609</v>
       </c>
       <c r="R5" t="n">
-        <v>6597049</v>
+        <v>6597045</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528399</v>
+        <v>123528299</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>78874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,37 +1111,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1150,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480697</v>
+        <v>480658</v>
       </c>
       <c r="R6" t="n">
-        <v>6597053</v>
+        <v>6597117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,11 +1178,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528200</v>
+        <v>123528399</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,29 +1217,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1261,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480609</v>
+        <v>480697</v>
       </c>
       <c r="R7" t="n">
-        <v>6597045</v>
+        <v>6597053</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1297,6 +1292,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig och välmående lokal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,62 +1324,70 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528290</v>
+        <v>123528192</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480646</v>
+        <v>480611</v>
       </c>
       <c r="R8" t="n">
-        <v>6597107</v>
+        <v>6597066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,11 +1420,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,70 +1446,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123528192</v>
+        <v>123528290</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480611</v>
+        <v>480646</v>
       </c>
       <c r="R9" t="n">
-        <v>6597066</v>
+        <v>6597107</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Balgrop</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 58756-2020 artfynd.xlsx
+++ b/artfynd/A 58756-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528169</v>
+        <v>123528299</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480651</v>
+        <v>480658</v>
       </c>
       <c r="R2" t="n">
-        <v>6596942</v>
+        <v>6597117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528336</v>
+        <v>123528200</v>
       </c>
       <c r="B3" t="n">
-        <v>78874</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480674</v>
+        <v>480609</v>
       </c>
       <c r="R3" t="n">
-        <v>6597089</v>
+        <v>6597045</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528420</v>
+        <v>123528336</v>
       </c>
       <c r="B4" t="n">
         <v>78874</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480700</v>
+        <v>480674</v>
       </c>
       <c r="R4" t="n">
-        <v>6597049</v>
+        <v>6597089</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528200</v>
+        <v>123528169</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480609</v>
+        <v>480651</v>
       </c>
       <c r="R5" t="n">
-        <v>6597045</v>
+        <v>6596942</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528299</v>
+        <v>123528420</v>
       </c>
       <c r="B6" t="n">
         <v>78874</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480658</v>
+        <v>480700</v>
       </c>
       <c r="R6" t="n">
-        <v>6597117</v>
+        <v>6597049</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
